--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/ashland.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/ashland.xlsx
@@ -278,7 +278,7 @@
         <family/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">That is a "land deed". Mysillia is looking for pioneers and we're giving away land for free to promising adventurers.
+      <t xml:space="preserve">That is a "land deed". Mysilia is looking for pioneers and we're giving away land for free to promising adventurers.
 </t>
     </r>
     <r>
@@ -297,7 +297,7 @@
 つまり、君に命を助けた恩を着せ、あわよくば金のコインが飛び交う景気の良い街の一つでも作ってもらおうという魂胆さ。 （男はニヤリと笑った）</t>
   </si>
   <si>
-    <t xml:space="preserve">I'm not going to lie. Fiama and I serve Mysillia and Mysillia needs allies and coins.
+    <t xml:space="preserve">I'm not going to lie. Fiama and I serve Mysillia and Mysilia needs allies and coins.
 So my secret intention here is to emphasize the favor we have done to you in a hope you might be driven to make a blooming town or two for us. (He grins at you gleefully) </t>
   </si>
   <si>
@@ -503,7 +503,7 @@
   </si>
   <si>
     <t xml:space="preserve">Click the inventory icon at the lower right corner of your screen to open your backpack. Items in your backpack can be moved freely by dragging.
-Items such as food and books can be used directly by right-clicking on them. You can also middle-click(or press R key) an item to display all actions you can perform on the item.
+Items such as food and books can be used directly by right-clicking on them. You can also middle-click (or press R key) an item to display all actions you can perform on the item.
 The slots in the lower screen toolbar can be easily swapped with the mouse wheel, making it easy to switch between frequently used items and tools.</t>
   </si>
   <si>
@@ -849,7 +849,7 @@
   </si>
   <si>
     <t xml:space="preserve">Take the bill you received to the capital of Mysilia. There is a tax box in the town hall. There, you can drop off the bill along with the money you have been billed.
-It will be truely pleasant to have a weight lifted off your shoulders. Why don't you go to the market in Mysilia and buy some souvenirs after you paid your tax?</t>
+It will be truly pleasant to have a weight lifted off your shoulders. Why don't you go to the market in Mysilia and buy some souvenirs after you paid your tax?</t>
   </si>
   <si>
     <t xml:space="preserve">税金だけでなく、様々な名目で君は将来請求書を受け取るようになる。支払い方法はみな同じだから安心してくれ。ただ、支払期限には留意することだ。請求書の滞納は君の評判を落とすだけでなく、役所の連中は実力行使もいとわないからな。</t>
